--- a/site/Active-Directory-ServiceNow-Group-Sync-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-ServiceNow-Group-Sync-Integration-Guide/headings.xlsx
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
